--- a/DOM/Energy/A2_Structure_Lists.xlsx
+++ b/DOM/Energy/A2_Structure_Lists.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
   <si>
     <t>Year</t>
   </si>
@@ -40,7 +40,10 @@
     <t>EXTT_CRU</t>
   </si>
   <si>
-    <t>EXTT_LPG</t>
+    <t>EXTT_NGS</t>
+  </si>
+  <si>
+    <t>PRO_COA</t>
   </si>
   <si>
     <t>DIST_FIR</t>
@@ -109,121 +112,7 @@
     <t>PPPVD</t>
   </si>
   <si>
-    <t>PPPVDS</t>
-  </si>
-  <si>
-    <t>SOIALL</t>
-  </si>
-  <si>
-    <t>IMPRIC</t>
-  </si>
-  <si>
-    <t>IMPBAN</t>
-  </si>
-  <si>
-    <t>IMPSGC</t>
-  </si>
-  <si>
-    <t>IMPCOC</t>
-  </si>
-  <si>
-    <t>IMPTRVEG</t>
-  </si>
-  <si>
-    <t>IMPCAF</t>
-  </si>
-  <si>
-    <t>IMPLEG</t>
-  </si>
-  <si>
-    <t>IMPROT</t>
-  </si>
-  <si>
-    <t>IMPFRT</t>
-  </si>
-  <si>
-    <t>IMPCER</t>
-  </si>
-  <si>
-    <t>IMPOTP</t>
-  </si>
-  <si>
-    <t>IMPLEC</t>
-  </si>
-  <si>
-    <t>IMPCARAVI</t>
-  </si>
-  <si>
-    <t>IMPCARBOV</t>
-  </si>
-  <si>
-    <t>IMPOTRCARPRO</t>
-  </si>
-  <si>
-    <t>IMPCARPOR</t>
-  </si>
-  <si>
-    <t>IMPOTRCAR</t>
-  </si>
-  <si>
-    <t>INORG_RCY_OS</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>COMPOST</t>
-  </si>
-  <si>
-    <t>LANDFILL</t>
-  </si>
-  <si>
-    <t>NO_CONTR_OD</t>
-  </si>
-  <si>
-    <t>COPROC</t>
-  </si>
-  <si>
-    <t>INCIN</t>
-  </si>
-  <si>
-    <t>OPEN_BURN</t>
-  </si>
-  <si>
-    <t>SIT_CLAN</t>
-  </si>
-  <si>
-    <t>AERO_PTAR</t>
-  </si>
-  <si>
-    <t>AERO_PTAR_RU</t>
-  </si>
-  <si>
-    <t>ANAE_LAGN</t>
-  </si>
-  <si>
-    <t>ANAE_LAGN_RU</t>
-  </si>
-  <si>
-    <t>SEPT_SYST</t>
-  </si>
-  <si>
-    <t>LATR</t>
-  </si>
-  <si>
-    <t>EFLT_DISC</t>
-  </si>
-  <si>
-    <t>SEWER_NO_T</t>
-  </si>
-  <si>
-    <t>RAW_MAT_CLK</t>
-  </si>
-  <si>
-    <t>RAW_MAT_CEM</t>
-  </si>
-  <si>
-    <t>IMP_STOR</t>
+    <t>PPDHYD</t>
   </si>
   <si>
     <t>REF_DSL</t>
@@ -265,6 +154,36 @@
     <t>PPICEGASFOI</t>
   </si>
   <si>
+    <t>PPADSL</t>
+  </si>
+  <si>
+    <t>PPAFOI</t>
+  </si>
+  <si>
+    <t>PPANGS</t>
+  </si>
+  <si>
+    <t>PPDBIM</t>
+  </si>
+  <si>
+    <t>PPDBGS</t>
+  </si>
+  <si>
+    <t>PPDDSL</t>
+  </si>
+  <si>
+    <t>PPDFOI</t>
+  </si>
+  <si>
+    <t>PPDNGS</t>
+  </si>
+  <si>
+    <t>PPDGSL</t>
+  </si>
+  <si>
+    <t>PPDGLP</t>
+  </si>
+  <si>
     <t>ELE_TRANS</t>
   </si>
   <si>
@@ -277,129 +196,6 @@
     <t>HYD_DIST</t>
   </si>
   <si>
-    <t>LU_FOR</t>
-  </si>
-  <si>
-    <t>LU_AGR</t>
-  </si>
-  <si>
-    <t>LU_GAN</t>
-  </si>
-  <si>
-    <t>LU_LATHUM</t>
-  </si>
-  <si>
-    <t>LU_DCON</t>
-  </si>
-  <si>
-    <t>LU_WET</t>
-  </si>
-  <si>
-    <t>LU_DRY</t>
-  </si>
-  <si>
-    <t>AG_RIC</t>
-  </si>
-  <si>
-    <t>AG_BAN</t>
-  </si>
-  <si>
-    <t>AG_SGC</t>
-  </si>
-  <si>
-    <t>AG_COC</t>
-  </si>
-  <si>
-    <t>AG_CAF</t>
-  </si>
-  <si>
-    <t>AG_LEG</t>
-  </si>
-  <si>
-    <t>AG_ROT</t>
-  </si>
-  <si>
-    <t>AG_FRT</t>
-  </si>
-  <si>
-    <t>AGR_CER</t>
-  </si>
-  <si>
-    <t>AG_TRVEG</t>
-  </si>
-  <si>
-    <t>AGR_OTP</t>
-  </si>
-  <si>
-    <t>GA_LEC</t>
-  </si>
-  <si>
-    <t>GA_CARAVI</t>
-  </si>
-  <si>
-    <t>GA_CARBOV</t>
-  </si>
-  <si>
-    <t>GA_CARPOR</t>
-  </si>
-  <si>
-    <t>GA_OTRCARPRO</t>
-  </si>
-  <si>
-    <t>GA_OTRCAR</t>
-  </si>
-  <si>
-    <t>OSS_INORG</t>
-  </si>
-  <si>
-    <t>OSS_ORG</t>
-  </si>
-  <si>
-    <t>NO_OSS_BLEND</t>
-  </si>
-  <si>
-    <t>NO_OSS_NO_COLL</t>
-  </si>
-  <si>
-    <t>INORG_DCOLL</t>
-  </si>
-  <si>
-    <t>ORG_DCOLL</t>
-  </si>
-  <si>
-    <t>BLEND_NO_DCOLL</t>
-  </si>
-  <si>
-    <t>BLEND_NO_COLL</t>
-  </si>
-  <si>
-    <t>INORG_SS</t>
-  </si>
-  <si>
-    <t>ORG_SS</t>
-  </si>
-  <si>
-    <t>NO_SS</t>
-  </si>
-  <si>
-    <t>WWWT</t>
-  </si>
-  <si>
-    <t>WWWOT</t>
-  </si>
-  <si>
-    <t>SEWERWW</t>
-  </si>
-  <si>
-    <t>DIRECT_DISC</t>
-  </si>
-  <si>
-    <t>PROD_CLK_TRAD</t>
-  </si>
-  <si>
-    <t>PROD_CEM</t>
-  </si>
-  <si>
     <t>T5DSLCOM</t>
   </si>
   <si>
@@ -418,6 +214,9 @@
     <t>T5FIRCOM</t>
   </si>
   <si>
+    <t>T5BIMCOM</t>
+  </si>
+  <si>
     <t>T5DSLIND</t>
   </si>
   <si>
@@ -502,117 +301,6 @@
     <t>T5ELEAGR</t>
   </si>
   <si>
-    <t>T5RICAGR</t>
-  </si>
-  <si>
-    <t>T5BANAGR</t>
-  </si>
-  <si>
-    <t>T5SGCAGR</t>
-  </si>
-  <si>
-    <t>T5COCAGR</t>
-  </si>
-  <si>
-    <t>T5CAFAGR</t>
-  </si>
-  <si>
-    <t>T5LEGAGR</t>
-  </si>
-  <si>
-    <t>T5ROTAGR</t>
-  </si>
-  <si>
-    <t>T5FRTAGR</t>
-  </si>
-  <si>
-    <t>T5CERAGR</t>
-  </si>
-  <si>
-    <t>T5TRVEGAGR</t>
-  </si>
-  <si>
-    <t>T5OTPAGR</t>
-  </si>
-  <si>
-    <t>T5LECGAN</t>
-  </si>
-  <si>
-    <t>T5CARAVIGAN</t>
-  </si>
-  <si>
-    <t>T5CARBOVGAN</t>
-  </si>
-  <si>
-    <t>T5CARPORGAN</t>
-  </si>
-  <si>
-    <t>T5OTRCARPROGAN</t>
-  </si>
-  <si>
-    <t>T5OTRCARGAN</t>
-  </si>
-  <si>
-    <t>T5RICAGREXP</t>
-  </si>
-  <si>
-    <t>T5BANAGREXP</t>
-  </si>
-  <si>
-    <t>T5SGCAGREXP</t>
-  </si>
-  <si>
-    <t>T5COCAGREXP</t>
-  </si>
-  <si>
-    <t>T5CAFAGREXP</t>
-  </si>
-  <si>
-    <t>T5LEGAGREXP</t>
-  </si>
-  <si>
-    <t>T5ROTAGREXP</t>
-  </si>
-  <si>
-    <t>T5FRTAGREXP</t>
-  </si>
-  <si>
-    <t>T5CERAGREXP</t>
-  </si>
-  <si>
-    <t>T5TRVEGAGREXP</t>
-  </si>
-  <si>
-    <t>T5OTPAGREXP</t>
-  </si>
-  <si>
-    <t>T5LECGANEXP</t>
-  </si>
-  <si>
-    <t>T5CARAVIGANEXP</t>
-  </si>
-  <si>
-    <t>T5CARBOVGANEXP</t>
-  </si>
-  <si>
-    <t>T5CARPORGANEXP</t>
-  </si>
-  <si>
-    <t>T5OTRCARPROGANEXP</t>
-  </si>
-  <si>
-    <t>T5OTRCARGANEXP</t>
-  </si>
-  <si>
-    <t>T5TSWTSW</t>
-  </si>
-  <si>
-    <t>T5TWWTWW</t>
-  </si>
-  <si>
-    <t>T5CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
     <t>T4DSL_PRI</t>
   </si>
   <si>
@@ -820,6 +508,9 @@
     <t>TRYLFHD</t>
   </si>
   <si>
+    <t>TRXBUSEFIELE</t>
+  </si>
+  <si>
     <t>Techs_Auto</t>
   </si>
   <si>
@@ -856,6 +547,9 @@
     <t>Techs_Li_Freight</t>
   </si>
   <si>
+    <t>Techs_Bus_Efi</t>
+  </si>
+  <si>
     <t>TRANE6NOMOT</t>
   </si>
   <si>
@@ -865,10 +559,13 @@
     <t>All</t>
   </si>
   <si>
-    <t>E0_CRU</t>
-  </si>
-  <si>
-    <t>E0_LPG</t>
+    <t>E1CRU</t>
+  </si>
+  <si>
+    <t>E1NGS</t>
+  </si>
+  <si>
+    <t>E1COA</t>
   </si>
   <si>
     <t>E1FIR</t>
@@ -880,12 +577,6 @@
     <t>E1BGS</t>
   </si>
   <si>
-    <t>E1CRU</t>
-  </si>
-  <si>
-    <t>E1NGS</t>
-  </si>
-  <si>
     <t>E1DSL</t>
   </si>
   <si>
@@ -904,9 +595,6 @@
     <t>E1KER</t>
   </si>
   <si>
-    <t>E1COA</t>
-  </si>
-  <si>
     <t>E1ELE</t>
   </si>
   <si>
@@ -916,141 +604,15 @@
     <t>E3ELE</t>
   </si>
   <si>
-    <t>E1_SOI</t>
-  </si>
-  <si>
-    <t>E3_RIC</t>
-  </si>
-  <si>
-    <t>E3_BAN</t>
-  </si>
-  <si>
-    <t>E3_SGC</t>
-  </si>
-  <si>
-    <t>E3_COC</t>
-  </si>
-  <si>
-    <t>E3_TRVEG</t>
-  </si>
-  <si>
-    <t>E3_CAF</t>
-  </si>
-  <si>
-    <t>E3_LEG</t>
-  </si>
-  <si>
-    <t>E3_ROT</t>
-  </si>
-  <si>
-    <t>E3_FRT</t>
-  </si>
-  <si>
-    <t>E3_CER</t>
-  </si>
-  <si>
-    <t>E3_OTP</t>
-  </si>
-  <si>
-    <t>E3_LEC</t>
-  </si>
-  <si>
-    <t>E3_CARAVI</t>
-  </si>
-  <si>
-    <t>E3_CARBOV</t>
-  </si>
-  <si>
-    <t>E3_OTRCARPRO</t>
-  </si>
-  <si>
-    <t>E3_CARPOR</t>
-  </si>
-  <si>
-    <t>E3_OTRCAR</t>
-  </si>
-  <si>
-    <t>NO_OSS</t>
-  </si>
-  <si>
-    <t>NO_COLL_SDF</t>
-  </si>
-  <si>
-    <t>WWT</t>
-  </si>
-  <si>
-    <t>WWOT</t>
-  </si>
-  <si>
-    <t>CLK_PROD</t>
-  </si>
-  <si>
     <t>E2ELE</t>
   </si>
   <si>
     <t>E2HYDG</t>
   </si>
   <si>
-    <t>E2_FOR</t>
-  </si>
-  <si>
-    <t>E2_CUL</t>
-  </si>
-  <si>
-    <t>E2_PAS</t>
-  </si>
-  <si>
-    <t>COLL_INORG</t>
-  </si>
-  <si>
-    <t>COLL_ORG</t>
-  </si>
-  <si>
-    <t>COLL_BLEND</t>
-  </si>
-  <si>
-    <t>NO_COLL</t>
-  </si>
-  <si>
-    <t>INORGSS</t>
-  </si>
-  <si>
-    <t>ORGSS</t>
-  </si>
-  <si>
-    <t>NOSS</t>
-  </si>
-  <si>
-    <t>SEWER</t>
-  </si>
-  <si>
-    <t>DIRECTW</t>
-  </si>
-  <si>
     <t>E3HYD</t>
   </si>
   <si>
-    <t>E3_LATHUM</t>
-  </si>
-  <si>
-    <t>E3_DCON</t>
-  </si>
-  <si>
-    <t>E3_WET</t>
-  </si>
-  <si>
-    <t>E3_DRY</t>
-  </si>
-  <si>
-    <t>TSW</t>
-  </si>
-  <si>
-    <t>TWW</t>
-  </si>
-  <si>
-    <t>CEM_PROD</t>
-  </si>
-  <si>
     <t>E5COMDSL</t>
   </si>
   <si>
@@ -1069,6 +631,9 @@
     <t>E5COMFIR</t>
   </si>
   <si>
+    <t>E5COMBIM</t>
+  </si>
+  <si>
     <t>E5INDDSL</t>
   </si>
   <si>
@@ -1153,117 +718,6 @@
     <t>E5AGRELE</t>
   </si>
   <si>
-    <t>E5AGRRIC</t>
-  </si>
-  <si>
-    <t>E5AGRBAN</t>
-  </si>
-  <si>
-    <t>E5AGRSGC</t>
-  </si>
-  <si>
-    <t>E5AGRCOC</t>
-  </si>
-  <si>
-    <t>E5AGRCAF</t>
-  </si>
-  <si>
-    <t>E5AGRLEG</t>
-  </si>
-  <si>
-    <t>E5AGRROT</t>
-  </si>
-  <si>
-    <t>E5AGRFRT</t>
-  </si>
-  <si>
-    <t>E5AGRCER</t>
-  </si>
-  <si>
-    <t>E5AGRTRVEG</t>
-  </si>
-  <si>
-    <t>E5AGROTP</t>
-  </si>
-  <si>
-    <t>E5GANLEC</t>
-  </si>
-  <si>
-    <t>E5GANCARAVI</t>
-  </si>
-  <si>
-    <t>E5GANCARBOV</t>
-  </si>
-  <si>
-    <t>E5GANCARPOR</t>
-  </si>
-  <si>
-    <t>E5GANOTRCARPRO</t>
-  </si>
-  <si>
-    <t>E5GANOTRCAR</t>
-  </si>
-  <si>
-    <t>E5AGREXPRIC</t>
-  </si>
-  <si>
-    <t>E5AGREXPBAN</t>
-  </si>
-  <si>
-    <t>E5AGREXPSGC</t>
-  </si>
-  <si>
-    <t>E5AGREXPCOC</t>
-  </si>
-  <si>
-    <t>E5AGREXPCAF</t>
-  </si>
-  <si>
-    <t>E5AGREXPLEG</t>
-  </si>
-  <si>
-    <t>E5AGREXPROT</t>
-  </si>
-  <si>
-    <t>E5AGREXPFRT</t>
-  </si>
-  <si>
-    <t>E5AGREXPCER</t>
-  </si>
-  <si>
-    <t>E5AGREXPTRVEG</t>
-  </si>
-  <si>
-    <t>E5AGREXPOTP</t>
-  </si>
-  <si>
-    <t>E5GANEXPLEC</t>
-  </si>
-  <si>
-    <t>E5GANEXPCARAVI</t>
-  </si>
-  <si>
-    <t>E5GANEXPCARBOV</t>
-  </si>
-  <si>
-    <t>E5GANEXPCARPOR</t>
-  </si>
-  <si>
-    <t>E5GANEXPOTRCARPRO</t>
-  </si>
-  <si>
-    <t>E5GANEXPOTRCAR</t>
-  </si>
-  <si>
-    <t>E5TSWTSW</t>
-  </si>
-  <si>
-    <t>E5TWWTWW</t>
-  </si>
-  <si>
-    <t>E5CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
     <t>E4DSL_PRI</t>
   </si>
   <si>
@@ -1375,6 +829,9 @@
     <t>E5TRYLF</t>
   </si>
   <si>
+    <t>E5TRXBUSEFI</t>
+  </si>
+  <si>
     <t>E6TDPASPRI</t>
   </si>
   <si>
@@ -1393,64 +850,28 @@
     <t>E6TRNOMOT</t>
   </si>
   <si>
-    <t>CO2e_AFOLU</t>
-  </si>
-  <si>
     <t>CO2e_PP</t>
   </si>
   <si>
-    <t>CONTUR</t>
-  </si>
-  <si>
-    <t>CONVAR</t>
-  </si>
-  <si>
-    <t>contam_agua</t>
-  </si>
-  <si>
-    <t>RM</t>
-  </si>
-  <si>
-    <t>CO2e_WASTE</t>
-  </si>
-  <si>
-    <t>CO2e_HFC</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>salud_residuos</t>
-  </si>
-  <si>
-    <t>CO2e_PIUP</t>
-  </si>
-  <si>
-    <t>CONHICK</t>
-  </si>
-  <si>
-    <t>DAPANI</t>
+    <t>CO2e_sources</t>
+  </si>
+  <si>
+    <t>CO2e_AP</t>
+  </si>
+  <si>
+    <t>CO2e_FUG</t>
+  </si>
+  <si>
+    <t>CO2e_DE</t>
+  </si>
+  <si>
+    <t>CO2e_CARBONERAS</t>
   </si>
   <si>
     <t>CO2e_TRN</t>
-  </si>
-  <si>
-    <t>CO2e_sources</t>
-  </si>
-  <si>
-    <t>CO2e_DE</t>
-  </si>
-  <si>
-    <t>FERT_ORG</t>
-  </si>
-  <si>
-    <t>turismo_residuos</t>
-  </si>
-  <si>
-    <t>CONHAB</t>
-  </si>
-  <si>
-    <t>RESHID</t>
   </si>
   <si>
     <t>RD</t>
@@ -1811,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G276"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1845,19 +1266,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>459</v>
+        <v>278</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>479</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1868,10 +1289,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>460</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1882,10 +1303,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>461</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1896,10 +1317,10 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>462</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1910,10 +1331,10 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>185</v>
       </c>
       <c r="E6" t="s">
-        <v>463</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1924,10 +1345,10 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>464</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1938,10 +1359,10 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>187</v>
       </c>
       <c r="E8" t="s">
-        <v>465</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1952,10 +1373,10 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="E9" t="s">
-        <v>466</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1966,10 +1387,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
-      </c>
-      <c r="E10" t="s">
-        <v>467</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1980,10 +1398,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>292</v>
-      </c>
-      <c r="E11" t="s">
-        <v>468</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1994,10 +1409,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>293</v>
-      </c>
-      <c r="E12" t="s">
-        <v>469</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2008,10 +1420,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E13" t="s">
-        <v>470</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2022,10 +1431,7 @@
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>295</v>
-      </c>
-      <c r="E14" t="s">
-        <v>471</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2036,10 +1442,7 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>296</v>
-      </c>
-      <c r="E15" t="s">
-        <v>472</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2050,13 +1453,10 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>297</v>
-      </c>
-      <c r="E16" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>2033</v>
       </c>
@@ -2064,13 +1464,10 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>298</v>
-      </c>
-      <c r="E17" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>2034</v>
       </c>
@@ -2078,13 +1475,10 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>299</v>
-      </c>
-      <c r="E18" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>2035</v>
       </c>
@@ -2092,13 +1486,10 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>300</v>
-      </c>
-      <c r="E19" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>2036</v>
       </c>
@@ -2106,13 +1497,10 @@
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>301</v>
-      </c>
-      <c r="E20" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>2037</v>
       </c>
@@ -2120,13 +1508,10 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>302</v>
-      </c>
-      <c r="E21" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>2038</v>
       </c>
@@ -2134,10 +1519,10 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>2039</v>
       </c>
@@ -2145,10 +1530,10 @@
         <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>2040</v>
       </c>
@@ -2156,10 +1541,10 @@
         <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>2041</v>
       </c>
@@ -2167,10 +1552,10 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>2042</v>
       </c>
@@ -2178,10 +1563,10 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>2043</v>
       </c>
@@ -2189,10 +1574,10 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>2044</v>
       </c>
@@ -2200,10 +1585,10 @@
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>2045</v>
       </c>
@@ -2211,10 +1596,10 @@
         <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>2046</v>
       </c>
@@ -2222,10 +1607,10 @@
         <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>2047</v>
       </c>
@@ -2233,10 +1618,10 @@
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>2048</v>
       </c>
@@ -2244,7 +1629,7 @@
         <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>313</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2255,7 +1640,7 @@
         <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2266,7 +1651,7 @@
         <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>315</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2274,7 +1659,7 @@
         <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>316</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2282,7 +1667,7 @@
         <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>317</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2290,7 +1675,7 @@
         <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2298,7 +1683,7 @@
         <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2306,7 +1691,7 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>318</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2314,7 +1699,7 @@
         <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>319</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2322,7 +1707,7 @@
         <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>320</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2330,7 +1715,7 @@
         <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>321</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2338,7 +1723,7 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2346,7 +1731,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2354,7 +1739,7 @@
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>322</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2362,7 +1747,7 @@
         <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>323</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2370,7 +1755,7 @@
         <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>324</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2378,7 +1763,7 @@
         <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>325</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="2:4">
@@ -2386,7 +1771,7 @@
         <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>326</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="2:4">
@@ -2394,7 +1779,7 @@
         <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>327</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="2:4">
@@ -2402,7 +1787,7 @@
         <v>56</v>
       </c>
       <c r="D51" t="s">
-        <v>328</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" spans="2:4">
@@ -2410,7 +1795,7 @@
         <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>329</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="2:4">
@@ -2418,7 +1803,7 @@
         <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>330</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="2:4">
@@ -2426,7 +1811,7 @@
         <v>59</v>
       </c>
       <c r="D54" t="s">
-        <v>331</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="2:4">
@@ -2434,7 +1819,7 @@
         <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="2:4">
@@ -2442,7 +1827,7 @@
         <v>61</v>
       </c>
       <c r="D56" t="s">
-        <v>333</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="2:4">
@@ -2450,7 +1835,7 @@
         <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>334</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="2:4">
@@ -2458,7 +1843,7 @@
         <v>63</v>
       </c>
       <c r="D58" t="s">
-        <v>335</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" spans="2:4">
@@ -2466,7 +1851,7 @@
         <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>336</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="2:4">
@@ -2474,7 +1859,7 @@
         <v>65</v>
       </c>
       <c r="D60" t="s">
-        <v>337</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="2:4">
@@ -2482,7 +1867,7 @@
         <v>66</v>
       </c>
       <c r="D61" t="s">
-        <v>338</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="2:4">
@@ -2490,7 +1875,7 @@
         <v>67</v>
       </c>
       <c r="D62" t="s">
-        <v>339</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" spans="2:4">
@@ -2498,7 +1883,7 @@
         <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>340</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="2:4">
@@ -2506,7 +1891,7 @@
         <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>341</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65" spans="2:4">
@@ -2514,7 +1899,7 @@
         <v>70</v>
       </c>
       <c r="D65" t="s">
-        <v>342</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="2:4">
@@ -2522,7 +1907,7 @@
         <v>71</v>
       </c>
       <c r="D66" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67" spans="2:4">
@@ -2530,7 +1915,7 @@
         <v>72</v>
       </c>
       <c r="D67" t="s">
-        <v>344</v>
+        <v>246</v>
       </c>
     </row>
     <row r="68" spans="2:4">
@@ -2538,7 +1923,7 @@
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>345</v>
+        <v>247</v>
       </c>
     </row>
     <row r="69" spans="2:4">
@@ -2546,7 +1931,7 @@
         <v>74</v>
       </c>
       <c r="D69" t="s">
-        <v>346</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" spans="2:4">
@@ -2554,7 +1939,7 @@
         <v>75</v>
       </c>
       <c r="D70" t="s">
-        <v>347</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="2:4">
@@ -2562,7 +1947,7 @@
         <v>76</v>
       </c>
       <c r="D71" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72" spans="2:4">
@@ -2570,7 +1955,7 @@
         <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>349</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" spans="2:4">
@@ -2578,7 +1963,7 @@
         <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>350</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74" spans="2:4">
@@ -2586,7 +1971,7 @@
         <v>79</v>
       </c>
       <c r="D74" t="s">
-        <v>351</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" spans="2:4">
@@ -2594,7 +1979,7 @@
         <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>352</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="2:4">
@@ -2602,7 +1987,7 @@
         <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>353</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" spans="2:4">
@@ -2610,7 +1995,7 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>354</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" spans="2:4">
@@ -2618,7 +2003,7 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>355</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79" spans="2:4">
@@ -2626,7 +2011,7 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>356</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="2:4">
@@ -2634,7 +2019,7 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>357</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="2:4">
@@ -2642,7 +2027,7 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>358</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="2:4">
@@ -2650,7 +2035,7 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>359</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="2:4">
@@ -2658,7 +2043,7 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>360</v>
+        <v>262</v>
       </c>
     </row>
     <row r="84" spans="2:4">
@@ -2666,7 +2051,7 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>361</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85" spans="2:4">
@@ -2674,7 +2059,7 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>362</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="2:4">
@@ -2682,7 +2067,7 @@
         <v>91</v>
       </c>
       <c r="D86" t="s">
-        <v>363</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87" spans="2:4">
@@ -2690,7 +2075,7 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>364</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" spans="2:4">
@@ -2698,7 +2083,7 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>365</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89" spans="2:4">
@@ -2706,7 +2091,7 @@
         <v>94</v>
       </c>
       <c r="D89" t="s">
-        <v>366</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="2:4">
@@ -2714,7 +2099,7 @@
         <v>95</v>
       </c>
       <c r="D90" t="s">
-        <v>367</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="2:4">
@@ -2722,7 +2107,7 @@
         <v>96</v>
       </c>
       <c r="D91" t="s">
-        <v>368</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="2:4">
@@ -2730,7 +2115,7 @@
         <v>97</v>
       </c>
       <c r="D92" t="s">
-        <v>369</v>
+        <v>271</v>
       </c>
     </row>
     <row r="93" spans="2:4">
@@ -2738,7 +2123,7 @@
         <v>98</v>
       </c>
       <c r="D93" t="s">
-        <v>370</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="2:4">
@@ -2746,7 +2131,7 @@
         <v>99</v>
       </c>
       <c r="D94" t="s">
-        <v>371</v>
+        <v>273</v>
       </c>
     </row>
     <row r="95" spans="2:4">
@@ -2754,7 +2139,7 @@
         <v>100</v>
       </c>
       <c r="D95" t="s">
-        <v>372</v>
+        <v>274</v>
       </c>
     </row>
     <row r="96" spans="2:4">
@@ -2762,7 +2147,7 @@
         <v>101</v>
       </c>
       <c r="D96" t="s">
-        <v>373</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97" spans="2:4">
@@ -2770,7 +2155,7 @@
         <v>102</v>
       </c>
       <c r="D97" t="s">
-        <v>374</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98" spans="2:4">
@@ -2778,1397 +2163,390 @@
         <v>103</v>
       </c>
       <c r="D98" t="s">
-        <v>375</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="B99" t="s">
         <v>104</v>
       </c>
-      <c r="D99" t="s">
-        <v>376</v>
-      </c>
     </row>
     <row r="100" spans="2:4">
       <c r="B100" t="s">
         <v>105</v>
       </c>
-      <c r="D100" t="s">
-        <v>377</v>
-      </c>
     </row>
     <row r="101" spans="2:4">
       <c r="B101" t="s">
         <v>106</v>
       </c>
-      <c r="D101" t="s">
-        <v>378</v>
-      </c>
     </row>
     <row r="102" spans="2:4">
       <c r="B102" t="s">
         <v>107</v>
       </c>
-      <c r="D102" t="s">
-        <v>379</v>
-      </c>
     </row>
     <row r="103" spans="2:4">
       <c r="B103" t="s">
         <v>108</v>
       </c>
-      <c r="D103" t="s">
-        <v>380</v>
-      </c>
     </row>
     <row r="104" spans="2:4">
       <c r="B104" t="s">
         <v>109</v>
       </c>
-      <c r="D104" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="105" spans="2:4">
       <c r="B105" t="s">
         <v>110</v>
       </c>
-      <c r="D105" t="s">
-        <v>382</v>
-      </c>
     </row>
     <row r="106" spans="2:4">
       <c r="B106" t="s">
         <v>111</v>
       </c>
-      <c r="D106" t="s">
-        <v>383</v>
-      </c>
     </row>
     <row r="107" spans="2:4">
       <c r="B107" t="s">
         <v>112</v>
       </c>
-      <c r="D107" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="108" spans="2:4">
       <c r="B108" t="s">
         <v>113</v>
       </c>
-      <c r="D108" t="s">
-        <v>385</v>
-      </c>
     </row>
     <row r="109" spans="2:4">
       <c r="B109" t="s">
         <v>114</v>
       </c>
-      <c r="D109" t="s">
-        <v>386</v>
-      </c>
     </row>
     <row r="110" spans="2:4">
       <c r="B110" t="s">
         <v>115</v>
       </c>
-      <c r="D110" t="s">
-        <v>387</v>
-      </c>
     </row>
     <row r="111" spans="2:4">
       <c r="B111" t="s">
         <v>116</v>
       </c>
-      <c r="D111" t="s">
-        <v>388</v>
-      </c>
     </row>
     <row r="112" spans="2:4">
       <c r="B112" t="s">
         <v>117</v>
       </c>
-      <c r="D112" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4">
+    </row>
+    <row r="113" spans="2:2">
       <c r="B113" t="s">
         <v>118</v>
       </c>
-      <c r="D113" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4">
+    </row>
+    <row r="114" spans="2:2">
       <c r="B114" t="s">
         <v>119</v>
       </c>
-      <c r="D114" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
+    </row>
+    <row r="115" spans="2:2">
       <c r="B115" t="s">
         <v>120</v>
       </c>
-      <c r="D115" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4">
+    </row>
+    <row r="116" spans="2:2">
       <c r="B116" t="s">
         <v>121</v>
       </c>
-      <c r="D116" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4">
+    </row>
+    <row r="117" spans="2:2">
       <c r="B117" t="s">
         <v>122</v>
       </c>
-      <c r="D117" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4">
+    </row>
+    <row r="118" spans="2:2">
       <c r="B118" t="s">
         <v>123</v>
       </c>
-      <c r="D118" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4">
+    </row>
+    <row r="119" spans="2:2">
       <c r="B119" t="s">
         <v>124</v>
       </c>
-      <c r="D119" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4">
+    </row>
+    <row r="120" spans="2:2">
       <c r="B120" t="s">
         <v>125</v>
       </c>
-      <c r="D120" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4">
+    </row>
+    <row r="121" spans="2:2">
       <c r="B121" t="s">
         <v>126</v>
       </c>
-      <c r="D121" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4">
+    </row>
+    <row r="122" spans="2:2">
       <c r="B122" t="s">
         <v>127</v>
       </c>
-      <c r="D122" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4">
+    </row>
+    <row r="123" spans="2:2">
       <c r="B123" t="s">
         <v>128</v>
       </c>
-      <c r="D123" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4">
+    </row>
+    <row r="124" spans="2:2">
       <c r="B124" t="s">
         <v>129</v>
       </c>
-      <c r="D124" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4">
+    </row>
+    <row r="125" spans="2:2">
       <c r="B125" t="s">
         <v>130</v>
       </c>
-      <c r="D125" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4">
+    </row>
+    <row r="126" spans="2:2">
       <c r="B126" t="s">
         <v>131</v>
       </c>
-      <c r="D126" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4">
+    </row>
+    <row r="127" spans="2:2">
       <c r="B127" t="s">
         <v>132</v>
       </c>
-      <c r="D127" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4">
+    </row>
+    <row r="128" spans="2:2">
       <c r="B128" t="s">
         <v>133</v>
       </c>
-      <c r="D128" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4">
+    </row>
+    <row r="129" spans="2:2">
       <c r="B129" t="s">
         <v>134</v>
       </c>
-      <c r="D129" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4">
+    </row>
+    <row r="130" spans="2:2">
       <c r="B130" t="s">
         <v>135</v>
       </c>
-      <c r="D130" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
+    </row>
+    <row r="131" spans="2:2">
       <c r="B131" t="s">
         <v>136</v>
       </c>
-      <c r="D131" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="132" spans="2:4">
+    </row>
+    <row r="132" spans="2:2">
       <c r="B132" t="s">
         <v>137</v>
       </c>
-      <c r="D132" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="133" spans="2:4">
+    </row>
+    <row r="133" spans="2:2">
       <c r="B133" t="s">
         <v>138</v>
       </c>
-      <c r="D133" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
+    </row>
+    <row r="134" spans="2:2">
       <c r="B134" t="s">
         <v>139</v>
       </c>
-      <c r="D134" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="135" spans="2:4">
+    </row>
+    <row r="135" spans="2:2">
       <c r="B135" t="s">
         <v>140</v>
       </c>
-      <c r="D135" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="136" spans="2:4">
+    </row>
+    <row r="136" spans="2:2">
       <c r="B136" t="s">
         <v>141</v>
       </c>
-      <c r="D136" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
+    </row>
+    <row r="137" spans="2:2">
       <c r="B137" t="s">
         <v>142</v>
       </c>
-      <c r="D137" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="138" spans="2:4">
+    </row>
+    <row r="138" spans="2:2">
       <c r="B138" t="s">
         <v>143</v>
       </c>
-      <c r="D138" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="139" spans="2:4">
+    </row>
+    <row r="139" spans="2:2">
       <c r="B139" t="s">
         <v>144</v>
       </c>
-      <c r="D139" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
+    </row>
+    <row r="140" spans="2:2">
       <c r="B140" t="s">
         <v>145</v>
       </c>
-      <c r="D140" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="141" spans="2:4">
+    </row>
+    <row r="141" spans="2:2">
       <c r="B141" t="s">
         <v>146</v>
       </c>
-      <c r="D141" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="142" spans="2:4">
+    </row>
+    <row r="142" spans="2:2">
       <c r="B142" t="s">
         <v>147</v>
       </c>
-      <c r="D142" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
+    </row>
+    <row r="143" spans="2:2">
       <c r="B143" t="s">
         <v>148</v>
       </c>
-      <c r="D143" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="144" spans="2:4">
+    </row>
+    <row r="144" spans="2:2">
       <c r="B144" t="s">
         <v>149</v>
       </c>
-      <c r="D144" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
+    </row>
+    <row r="145" spans="2:2">
       <c r="B145" t="s">
         <v>150</v>
       </c>
-      <c r="D145" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
+    </row>
+    <row r="146" spans="2:2">
       <c r="B146" t="s">
         <v>151</v>
       </c>
-      <c r="D146" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+    </row>
+    <row r="147" spans="2:2">
       <c r="B147" t="s">
         <v>152</v>
       </c>
-      <c r="D147" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+    </row>
+    <row r="148" spans="2:2">
       <c r="B148" t="s">
         <v>153</v>
       </c>
-      <c r="D148" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
+    </row>
+    <row r="149" spans="2:2">
       <c r="B149" t="s">
         <v>154</v>
       </c>
-      <c r="D149" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
+    </row>
+    <row r="150" spans="2:2">
       <c r="B150" t="s">
         <v>155</v>
       </c>
-      <c r="D150" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
+    </row>
+    <row r="151" spans="2:2">
       <c r="B151" t="s">
         <v>156</v>
       </c>
-      <c r="D151" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
+    </row>
+    <row r="152" spans="2:2">
       <c r="B152" t="s">
         <v>157</v>
       </c>
-      <c r="D152" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
+    </row>
+    <row r="153" spans="2:2">
       <c r="B153" t="s">
         <v>158</v>
       </c>
-      <c r="D153" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
+    </row>
+    <row r="154" spans="2:2">
       <c r="B154" t="s">
         <v>159</v>
       </c>
-      <c r="D154" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
+    </row>
+    <row r="155" spans="2:2">
       <c r="B155" t="s">
         <v>160</v>
       </c>
-      <c r="D155" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
+    </row>
+    <row r="156" spans="2:2">
       <c r="B156" t="s">
         <v>161</v>
       </c>
-      <c r="D156" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
+    </row>
+    <row r="157" spans="2:2">
       <c r="B157" t="s">
         <v>162</v>
       </c>
-      <c r="D157" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
+    </row>
+    <row r="158" spans="2:2">
       <c r="B158" t="s">
         <v>163</v>
       </c>
-      <c r="D158" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
+    </row>
+    <row r="159" spans="2:2">
       <c r="B159" t="s">
         <v>164</v>
       </c>
-      <c r="D159" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
+    </row>
+    <row r="160" spans="2:2">
       <c r="B160" t="s">
         <v>165</v>
       </c>
-      <c r="D160" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
+    </row>
+    <row r="161" spans="2:2">
       <c r="B161" t="s">
         <v>166</v>
       </c>
-      <c r="D161" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
+    </row>
+    <row r="162" spans="2:2">
       <c r="B162" t="s">
         <v>167</v>
       </c>
-      <c r="D162" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
+    </row>
+    <row r="163" spans="2:2">
       <c r="B163" t="s">
         <v>168</v>
       </c>
-      <c r="D163" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
+    </row>
+    <row r="164" spans="2:2">
       <c r="B164" t="s">
         <v>169</v>
       </c>
-      <c r="D164" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
+    </row>
+    <row r="165" spans="2:2">
       <c r="B165" t="s">
         <v>170</v>
       </c>
-      <c r="D165" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
+    </row>
+    <row r="166" spans="2:2">
       <c r="B166" t="s">
         <v>171</v>
       </c>
-      <c r="D166" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
+    </row>
+    <row r="167" spans="2:2">
       <c r="B167" t="s">
         <v>172</v>
       </c>
-      <c r="D167" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4">
+    </row>
+    <row r="168" spans="2:2">
       <c r="B168" t="s">
         <v>173</v>
       </c>
-      <c r="D168" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
+    </row>
+    <row r="169" spans="2:2">
       <c r="B169" t="s">
         <v>174</v>
       </c>
-      <c r="D169" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
+    </row>
+    <row r="170" spans="2:2">
       <c r="B170" t="s">
         <v>175</v>
       </c>
-      <c r="D170" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
+    </row>
+    <row r="171" spans="2:2">
       <c r="B171" t="s">
         <v>176</v>
       </c>
-      <c r="D171" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
+    </row>
+    <row r="172" spans="2:2">
       <c r="B172" t="s">
         <v>177</v>
       </c>
-      <c r="D172" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
+    </row>
+    <row r="173" spans="2:2">
       <c r="B173" t="s">
         <v>178</v>
       </c>
-      <c r="D173" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
+    </row>
+    <row r="174" spans="2:2">
       <c r="B174" t="s">
         <v>179</v>
-      </c>
-      <c r="D174" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" t="s">
-        <v>180</v>
-      </c>
-      <c r="D175" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4">
-      <c r="B176" t="s">
-        <v>181</v>
-      </c>
-      <c r="D176" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4">
-      <c r="B177" t="s">
-        <v>182</v>
-      </c>
-      <c r="D177" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4">
-      <c r="B178" t="s">
-        <v>183</v>
-      </c>
-      <c r="D178" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4">
-      <c r="B179" t="s">
-        <v>184</v>
-      </c>
-      <c r="D179" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4">
-      <c r="B180" t="s">
-        <v>185</v>
-      </c>
-      <c r="D180" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4">
-      <c r="B181" t="s">
-        <v>186</v>
-      </c>
-      <c r="D181" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4">
-      <c r="B182" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4">
-      <c r="B183" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4">
-      <c r="B184" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4">
-      <c r="B185" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="186" spans="2:4">
-      <c r="B186" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="187" spans="2:4">
-      <c r="B187" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4">
-      <c r="B188" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="189" spans="2:4">
-      <c r="B189" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4">
-      <c r="B190" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4">
-      <c r="B191" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="192" spans="2:4">
-      <c r="B192" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2">
-      <c r="B193" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="198" spans="2:2">
-      <c r="B198" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="199" spans="2:2">
-      <c r="B199" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="200" spans="2:2">
-      <c r="B200" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="201" spans="2:2">
-      <c r="B201" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="202" spans="2:2">
-      <c r="B202" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="205" spans="2:2">
-      <c r="B205" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="207" spans="2:2">
-      <c r="B207" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="208" spans="2:2">
-      <c r="B208" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="209" spans="2:2">
-      <c r="B209" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="210" spans="2:2">
-      <c r="B210" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="211" spans="2:2">
-      <c r="B211" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="212" spans="2:2">
-      <c r="B212" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="213" spans="2:2">
-      <c r="B213" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="214" spans="2:2">
-      <c r="B214" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="215" spans="2:2">
-      <c r="B215" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="216" spans="2:2">
-      <c r="B216" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="217" spans="2:2">
-      <c r="B217" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="218" spans="2:2">
-      <c r="B218" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2">
-      <c r="B219" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="220" spans="2:2">
-      <c r="B220" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="221" spans="2:2">
-      <c r="B221" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="222" spans="2:2">
-      <c r="B222" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="223" spans="2:2">
-      <c r="B223" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="224" spans="2:2">
-      <c r="B224" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="225" spans="2:2">
-      <c r="B225" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="226" spans="2:2">
-      <c r="B226" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="227" spans="2:2">
-      <c r="B227" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="228" spans="2:2">
-      <c r="B228" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="229" spans="2:2">
-      <c r="B229" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="230" spans="2:2">
-      <c r="B230" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="231" spans="2:2">
-      <c r="B231" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="232" spans="2:2">
-      <c r="B232" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="233" spans="2:2">
-      <c r="B233" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="234" spans="2:2">
-      <c r="B234" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="235" spans="2:2">
-      <c r="B235" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="236" spans="2:2">
-      <c r="B236" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="237" spans="2:2">
-      <c r="B237" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="238" spans="2:2">
-      <c r="B238" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="239" spans="2:2">
-      <c r="B239" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="240" spans="2:2">
-      <c r="B240" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="241" spans="2:2">
-      <c r="B241" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="242" spans="2:2">
-      <c r="B242" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="243" spans="2:2">
-      <c r="B243" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="244" spans="2:2">
-      <c r="B244" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="245" spans="2:2">
-      <c r="B245" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="246" spans="2:2">
-      <c r="B246" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="247" spans="2:2">
-      <c r="B247" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="248" spans="2:2">
-      <c r="B248" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="249" spans="2:2">
-      <c r="B249" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="250" spans="2:2">
-      <c r="B250" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="251" spans="2:2">
-      <c r="B251" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="252" spans="2:2">
-      <c r="B252" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="253" spans="2:2">
-      <c r="B253" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="254" spans="2:2">
-      <c r="B254" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="255" spans="2:2">
-      <c r="B255" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="256" spans="2:2">
-      <c r="B256" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="257" spans="2:2">
-      <c r="B257" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="258" spans="2:2">
-      <c r="B258" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="259" spans="2:2">
-      <c r="B259" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="260" spans="2:2">
-      <c r="B260" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="261" spans="2:2">
-      <c r="B261" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="262" spans="2:2">
-      <c r="B262" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="263" spans="2:2">
-      <c r="B263" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="264" spans="2:2">
-      <c r="B264" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="265" spans="2:2">
-      <c r="B265" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="266" spans="2:2">
-      <c r="B266" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="267" spans="2:2">
-      <c r="B267" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="268" spans="2:2">
-      <c r="B268" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="269" spans="2:2">
-      <c r="B269" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="270" spans="2:2">
-      <c r="B270" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="271" spans="2:2">
-      <c r="B271" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="272" spans="2:2">
-      <c r="B272" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="273" spans="2:2">
-      <c r="B273" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="274" spans="2:2">
-      <c r="B274" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="275" spans="2:2">
-      <c r="B275" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="276" spans="2:2">
-      <c r="B276" t="s">
-        <v>281</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1C5F874-530E-4BD1-838A-98E866407FD8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CF313A-0160-473C-B811-B5D65FDC7B9E}"/>
 </file>